--- a/从零开始学Slots/从零开始学Slots-17-数值篇-WaySlots(2).xlsx
+++ b/从零开始学Slots/从零开始学Slots-17-数值篇-WaySlots(2).xlsx
@@ -7090,6 +7090,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N133" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -8848,5 +8851,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:Q113" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-17-数值篇-WaySlots(2).xlsx
+++ b/从零开始学Slots/从零开始学Slots-17-数值篇-WaySlots(2).xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="178">
   <si>
     <r>
       <rPr>
@@ -6169,7 +6169,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6296,6 +6296,14 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -6685,8 +6693,8 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="28" t="s">
-        <v>21</v>
+      <c r="A26" s="32">
+        <v>5</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7156,8 +7164,8 @@
       <c r="B5" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>93</v>
+      <c r="C5" s="33">
+        <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7262,8 +7270,8 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
-        <v>112</v>
+      <c r="A14" s="33">
+        <v>10</v>
       </c>
       <c r="B14" s="17" t="n">
         <v>1781.25</v>
@@ -7540,8 +7548,8 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15" t="s">
-        <v>112</v>
+      <c r="A25" s="33">
+        <v>10</v>
       </c>
       <c r="B25" s="18" t="n">
         <f aca="false">(B14+B19)/$B$8*$B$7</f>
@@ -7731,8 +7739,8 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="15" t="s">
-        <v>112</v>
+      <c r="A33" s="33">
+        <v>10</v>
       </c>
       <c r="B33" s="18" t="n">
         <f aca="false">IFERROR((1-(B14+B19)/$B$8)^$B$7,0)</f>
@@ -7927,8 +7935,8 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="15" t="s">
-        <v>112</v>
+      <c r="A41" s="33">
+        <v>10</v>
       </c>
       <c r="B41" s="15" t="s">
         <v>132</v>
@@ -7952,8 +7960,8 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="15" t="s">
-        <v>112</v>
+      <c r="A42" s="33">
+        <v>10</v>
       </c>
       <c r="B42" s="15" t="s">
         <v>132</v>
@@ -7977,8 +7985,8 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="15" t="s">
-        <v>112</v>
+      <c r="A43" s="33">
+        <v>10</v>
       </c>
       <c r="B43" s="15" t="s">
         <v>132</v>

--- a/从零开始学Slots/从零开始学Slots-17-数值篇-WaySlots(2).xlsx
+++ b/从零开始学Slots/从零开始学Slots-17-数值篇-WaySlots(2).xlsx
@@ -5980,12 +5980,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="0.0000%"/>
+    <numFmt numFmtId="169" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -6169,7 +6170,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6303,6 +6304,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" applyNumberFormat="1" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7288,7 +7297,7 @@
       <c r="F14" s="17" t="n">
         <v>1781.25</v>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="34" t="n">
         <f aca="false">B14/$B$8</f>
         <v>0.178125</v>
       </c>
@@ -7318,7 +7327,7 @@
       <c r="F15" s="17" t="n">
         <v>1781.25</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="34" t="n">
         <f aca="false">B15/$B$8</f>
         <v>0.178125</v>
       </c>
@@ -7348,7 +7357,7 @@
       <c r="F16" s="17" t="n">
         <v>1781.25</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="34" t="n">
         <f aca="false">B16/$B$8</f>
         <v>0.178125</v>
       </c>
@@ -7378,7 +7387,7 @@
       <c r="F17" s="17" t="n">
         <v>1781.25</v>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="G17" s="34" t="n">
         <f aca="false">B17/$B$8</f>
         <v>0.178125</v>
       </c>
@@ -7408,7 +7417,7 @@
       <c r="F18" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="G18" s="18" t="n">
+      <c r="G18" s="34" t="n">
         <f aca="false">B18/$B$8</f>
         <v>0.2</v>
       </c>
@@ -7438,7 +7447,7 @@
       <c r="F19" s="17" t="n">
         <v>175</v>
       </c>
-      <c r="G19" s="18" t="n">
+      <c r="G19" s="34" t="n">
         <f aca="false">B19/$B$8</f>
         <v>0.0175</v>
       </c>
@@ -7468,7 +7477,7 @@
       <c r="F20" s="17" t="n">
         <v>700</v>
       </c>
-      <c r="G20" s="18" t="n">
+      <c r="G20" s="34" t="n">
         <f aca="false">B20/$B$8</f>
         <v>0.07</v>
       </c>
@@ -7503,7 +7512,7 @@
         <f aca="false">SUM(F14:F20)</f>
         <v>10000</v>
       </c>
-      <c r="G21" s="18" t="n">
+      <c r="G21" s="34" t="n">
         <f aca="false">SUM(G14:G20)</f>
         <v>1</v>
       </c>
@@ -7551,23 +7560,23 @@
       <c r="A25" s="33">
         <v>10</v>
       </c>
-      <c r="B25" s="18" t="n">
+      <c r="B25" s="34" t="n">
         <f aca="false">(B14+B19)/$B$8*$B$7</f>
         <v>0.586875</v>
       </c>
-      <c r="C25" s="18" t="n">
+      <c r="C25" s="34" t="n">
         <f aca="false">(C14+C19)/$B$8*$B$7</f>
         <v>0.586875</v>
       </c>
-      <c r="D25" s="18" t="n">
+      <c r="D25" s="34" t="n">
         <f aca="false">(D14+D19)/$B$8*$B$7</f>
         <v>0.586875</v>
       </c>
-      <c r="E25" s="18" t="n">
+      <c r="E25" s="34" t="n">
         <f aca="false">(E14+E19)/$B$8*$B$7</f>
         <v>0.586875</v>
       </c>
-      <c r="F25" s="18" t="n">
+      <c r="F25" s="34" t="n">
         <f aca="false">(F14+F19)/$B$8*$B$7</f>
         <v>0.586875</v>
       </c>
@@ -7582,23 +7591,23 @@
       <c r="A26" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="B26" s="18" t="n">
+      <c r="B26" s="34" t="n">
         <f aca="false">(B15+B19)/$B$8*$B$7</f>
         <v>0.586875</v>
       </c>
-      <c r="C26" s="18" t="n">
+      <c r="C26" s="34" t="n">
         <f aca="false">(C15+C19)/$B$8*$B$7</f>
         <v>0.586875</v>
       </c>
-      <c r="D26" s="18" t="n">
+      <c r="D26" s="34" t="n">
         <f aca="false">(D15+D19)/$B$8*$B$7</f>
         <v>0.586875</v>
       </c>
-      <c r="E26" s="18" t="n">
+      <c r="E26" s="34" t="n">
         <f aca="false">(E15+E19)/$B$8*$B$7</f>
         <v>0.586875</v>
       </c>
-      <c r="F26" s="18" t="n">
+      <c r="F26" s="34" t="n">
         <f aca="false">(F15+F19)/$B$8*$B$7</f>
         <v>0.586875</v>
       </c>
@@ -7613,23 +7622,23 @@
       <c r="A27" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="B27" s="18" t="n">
+      <c r="B27" s="34" t="n">
         <f aca="false">(B16+B19)/$B$8*$B$7</f>
         <v>0.586875</v>
       </c>
-      <c r="C27" s="18" t="n">
+      <c r="C27" s="34" t="n">
         <f aca="false">(C16+C19)/$B$8*$B$7</f>
         <v>0.586875</v>
       </c>
-      <c r="D27" s="18" t="n">
+      <c r="D27" s="34" t="n">
         <f aca="false">(D16+D19)/$B$8*$B$7</f>
         <v>0.586875</v>
       </c>
-      <c r="E27" s="18" t="n">
+      <c r="E27" s="34" t="n">
         <f aca="false">(E16+E19)/$B$8*$B$7</f>
         <v>0.586875</v>
       </c>
-      <c r="F27" s="18" t="n">
+      <c r="F27" s="34" t="n">
         <f aca="false">(F16+F19)/$B$8*$B$7</f>
         <v>0.586875</v>
       </c>
@@ -7644,23 +7653,23 @@
       <c r="A28" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B28" s="18" t="n">
+      <c r="B28" s="34" t="n">
         <f aca="false">(B17+B19)/$B$8*$B$7</f>
         <v>0.586875</v>
       </c>
-      <c r="C28" s="18" t="n">
+      <c r="C28" s="34" t="n">
         <f aca="false">(C17+C19)/$B$8*$B$7</f>
         <v>0.586875</v>
       </c>
-      <c r="D28" s="18" t="n">
+      <c r="D28" s="34" t="n">
         <f aca="false">(D17+D19)/$B$8*$B$7</f>
         <v>0.586875</v>
       </c>
-      <c r="E28" s="18" t="n">
+      <c r="E28" s="34" t="n">
         <f aca="false">(E17+E19)/$B$8*$B$7</f>
         <v>0.586875</v>
       </c>
-      <c r="F28" s="18" t="n">
+      <c r="F28" s="34" t="n">
         <f aca="false">(F17+F19)/$B$8*$B$7</f>
         <v>0.586875</v>
       </c>
@@ -7675,23 +7684,23 @@
       <c r="A29" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="B29" s="18" t="n">
+      <c r="B29" s="34" t="n">
         <f aca="false">(B18+B19)/$B$8*$B$7</f>
         <v>0.6525</v>
       </c>
-      <c r="C29" s="18" t="n">
+      <c r="C29" s="34" t="n">
         <f aca="false">(C18+C19)/$B$8*$B$7</f>
         <v>0.6525</v>
       </c>
-      <c r="D29" s="18" t="n">
+      <c r="D29" s="34" t="n">
         <f aca="false">(D18+D19)/$B$8*$B$7</f>
         <v>0.6525</v>
       </c>
-      <c r="E29" s="18" t="n">
+      <c r="E29" s="34" t="n">
         <f aca="false">(E18+E19)/$B$8*$B$7</f>
         <v>0.6525</v>
       </c>
-      <c r="F29" s="18" t="n">
+      <c r="F29" s="34" t="n">
         <f aca="false">(F18+F19)/$B$8*$B$7</f>
         <v>0.6525</v>
       </c>
@@ -7742,23 +7751,23 @@
       <c r="A33" s="33">
         <v>10</v>
       </c>
-      <c r="B33" s="18" t="n">
+      <c r="B33" s="34" t="n">
         <f aca="false">IFERROR((1-(B14+B19)/$B$8)^$B$7,0)</f>
         <v>0.520446021240235</v>
       </c>
-      <c r="C33" s="18" t="n">
+      <c r="C33" s="34" t="n">
         <f aca="false">IFERROR((1-(C14+C19)/$B$8)^$B$7,0)</f>
         <v>0.520446021240235</v>
       </c>
-      <c r="D33" s="18" t="n">
+      <c r="D33" s="34" t="n">
         <f aca="false">IFERROR((1-(D14+D19)/$B$8)^$B$7,0)</f>
         <v>0.520446021240235</v>
       </c>
-      <c r="E33" s="18" t="n">
+      <c r="E33" s="34" t="n">
         <f aca="false">IFERROR((1-(E14+E19)/$B$8)^$B$7,0)</f>
         <v>0.520446021240235</v>
       </c>
-      <c r="F33" s="18" t="n">
+      <c r="F33" s="34" t="n">
         <f aca="false">IFERROR((1-(F14+F19)/$B$8)^$B$7,0)</f>
         <v>0.520446021240235</v>
       </c>
@@ -7774,23 +7783,23 @@
       <c r="A34" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="B34" s="18" t="n">
+      <c r="B34" s="34" t="n">
         <f aca="false">IFERROR((1-(B15+B19)/$B$8)^$B$7,0)</f>
         <v>0.520446021240235</v>
       </c>
-      <c r="C34" s="18" t="n">
+      <c r="C34" s="34" t="n">
         <f aca="false">IFERROR((1-(C15+C19)/$B$8)^$B$7,0)</f>
         <v>0.520446021240235</v>
       </c>
-      <c r="D34" s="18" t="n">
+      <c r="D34" s="34" t="n">
         <f aca="false">IFERROR((1-(D15+D19)/$B$8)^$B$7,0)</f>
         <v>0.520446021240235</v>
       </c>
-      <c r="E34" s="18" t="n">
+      <c r="E34" s="34" t="n">
         <f aca="false">IFERROR((1-(E15+E19)/$B$8)^$B$7,0)</f>
         <v>0.520446021240235</v>
       </c>
-      <c r="F34" s="18" t="n">
+      <c r="F34" s="34" t="n">
         <f aca="false">IFERROR((1-(F15+F19)/$B$8)^$B$7,0)</f>
         <v>0.520446021240235</v>
       </c>
@@ -7806,23 +7815,23 @@
       <c r="A35" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="B35" s="18" t="n">
+      <c r="B35" s="34" t="n">
         <f aca="false">IFERROR((1-(B16+B19)/$B$8)^$B$7,0)</f>
         <v>0.520446021240235</v>
       </c>
-      <c r="C35" s="18" t="n">
+      <c r="C35" s="34" t="n">
         <f aca="false">IFERROR((1-(C16+C19)/$B$8)^$B$7,0)</f>
         <v>0.520446021240235</v>
       </c>
-      <c r="D35" s="18" t="n">
+      <c r="D35" s="34" t="n">
         <f aca="false">IFERROR((1-(D16+D19)/$B$8)^$B$7,0)</f>
         <v>0.520446021240235</v>
       </c>
-      <c r="E35" s="18" t="n">
+      <c r="E35" s="34" t="n">
         <f aca="false">IFERROR((1-(E16+E19)/$B$8)^$B$7,0)</f>
         <v>0.520446021240235</v>
       </c>
-      <c r="F35" s="18" t="n">
+      <c r="F35" s="34" t="n">
         <f aca="false">IFERROR((1-(F16+F19)/$B$8)^$B$7,0)</f>
         <v>0.520446021240235</v>
       </c>
@@ -7838,23 +7847,23 @@
       <c r="A36" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B36" s="18" t="n">
+      <c r="B36" s="34" t="n">
         <f aca="false">IFERROR((1-(B17+B19)/$B$8)^$B$7,0)</f>
         <v>0.520446021240235</v>
       </c>
-      <c r="C36" s="18" t="n">
+      <c r="C36" s="34" t="n">
         <f aca="false">IFERROR((1-(C17+C19)/$B$8)^$B$7,0)</f>
         <v>0.520446021240235</v>
       </c>
-      <c r="D36" s="18" t="n">
+      <c r="D36" s="34" t="n">
         <f aca="false">IFERROR((1-(D17+D19)/$B$8)^$B$7,0)</f>
         <v>0.520446021240235</v>
       </c>
-      <c r="E36" s="18" t="n">
+      <c r="E36" s="34" t="n">
         <f aca="false">IFERROR((1-(E17+E19)/$B$8)^$B$7,0)</f>
         <v>0.520446021240235</v>
       </c>
-      <c r="F36" s="18" t="n">
+      <c r="F36" s="34" t="n">
         <f aca="false">IFERROR((1-(F17+F19)/$B$8)^$B$7,0)</f>
         <v>0.520446021240235</v>
       </c>
@@ -7870,23 +7879,23 @@
       <c r="A37" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="B37" s="18" t="n">
+      <c r="B37" s="34" t="n">
         <f aca="false">IFERROR((1-(B18+B19)/$B$8)^$B$7,0)</f>
         <v>0.479129640625</v>
       </c>
-      <c r="C37" s="18" t="n">
+      <c r="C37" s="34" t="n">
         <f aca="false">IFERROR((1-(C18+C19)/$B$8)^$B$7,0)</f>
         <v>0.479129640625</v>
       </c>
-      <c r="D37" s="18" t="n">
+      <c r="D37" s="34" t="n">
         <f aca="false">IFERROR((1-(D18+D19)/$B$8)^$B$7,0)</f>
         <v>0.479129640625</v>
       </c>
-      <c r="E37" s="18" t="n">
+      <c r="E37" s="34" t="n">
         <f aca="false">IFERROR((1-(E18+E19)/$B$8)^$B$7,0)</f>
         <v>0.479129640625</v>
       </c>
-      <c r="F37" s="18" t="n">
+      <c r="F37" s="34" t="n">
         <f aca="false">IFERROR((1-(F18+F19)/$B$8)^$B$7,0)</f>
         <v>0.479129640625</v>
       </c>
@@ -7947,7 +7956,7 @@
       <c r="D41" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="E41" s="18" t="n">
+      <c r="E41" s="34" t="n">
         <f aca="false">INDEX(B25:B29,MATCH($A41,$A25:$A29,0))^C41*IF(C41=5,1,INDEX(B33:B37,MATCH($A41,$A25:$A29,0)))</f>
         <v>0.105199220441902</v>
       </c>
@@ -7972,7 +7981,7 @@
       <c r="D42" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="E42" s="18" t="n">
+      <c r="E42" s="34" t="n">
         <f aca="false">INDEX(B25:B29,MATCH($A42,$A25:$A29,0))^C42*IF(C42=5,1,INDEX(B33:B37,MATCH($A42,$A25:$A29,0)))</f>
         <v>0.0617387924968411</v>
       </c>
@@ -7997,7 +8006,7 @@
       <c r="D43" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="E43" s="18" t="n">
+      <c r="E43" s="34" t="n">
         <f aca="false">INDEX(B25:B29,MATCH($A43,$A25:$A29,0))^C43*IF(C43=5,1,INDEX(B33:B37,MATCH($A43,$A25:$A29,0)))</f>
         <v>0.0696190428360652</v>
       </c>
@@ -8022,7 +8031,7 @@
       <c r="D44" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="E44" s="18" t="n">
+      <c r="E44" s="34" t="n">
         <f aca="false">INDEX(B25:B29,MATCH($A44,$A25:$A29,0))^C44*IF(C44=5,1,INDEX(B33:B37,MATCH($A44,$A25:$A29,0)))</f>
         <v>0.105199220441902</v>
       </c>
@@ -8047,7 +8056,7 @@
       <c r="D45" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="E45" s="18" t="n">
+      <c r="E45" s="34" t="n">
         <f aca="false">INDEX(B25:B29,MATCH($A45,$A25:$A29,0))^C45*IF(C45=5,1,INDEX(B33:B37,MATCH($A45,$A25:$A29,0)))</f>
         <v>0.0617387924968411</v>
       </c>
@@ -8072,7 +8081,7 @@
       <c r="D46" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="E46" s="18" t="n">
+      <c r="E46" s="34" t="n">
         <f aca="false">INDEX(B25:B29,MATCH($A46,$A25:$A29,0))^C46*IF(C46=5,1,INDEX(B33:B37,MATCH($A46,$A25:$A29,0)))</f>
         <v>0.0696190428360652</v>
       </c>
@@ -8097,7 +8106,7 @@
       <c r="D47" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="E47" s="18" t="n">
+      <c r="E47" s="34" t="n">
         <f aca="false">INDEX(B25:B29,MATCH($A47,$A25:$A29,0))^C47*IF(C47=5,1,INDEX(B33:B37,MATCH($A47,$A25:$A29,0)))</f>
         <v>0.105199220441902</v>
       </c>
@@ -8122,7 +8131,7 @@
       <c r="D48" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="E48" s="18" t="n">
+      <c r="E48" s="34" t="n">
         <f aca="false">INDEX(B25:B29,MATCH($A48,$A25:$A29,0))^C48*IF(C48=5,1,INDEX(B33:B37,MATCH($A48,$A25:$A29,0)))</f>
         <v>0.0617387924968411</v>
       </c>
@@ -8147,7 +8156,7 @@
       <c r="D49" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="E49" s="18" t="n">
+      <c r="E49" s="34" t="n">
         <f aca="false">INDEX(B25:B29,MATCH($A49,$A25:$A29,0))^C49*IF(C49=5,1,INDEX(B33:B37,MATCH($A49,$A25:$A29,0)))</f>
         <v>0.0696190428360652</v>
       </c>
@@ -8172,7 +8181,7 @@
       <c r="D50" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="E50" s="18" t="n">
+      <c r="E50" s="34" t="n">
         <f aca="false">INDEX(B25:B29,MATCH($A50,$A25:$A29,0))^C50*IF(C50=5,1,INDEX(B33:B37,MATCH($A50,$A25:$A29,0)))</f>
         <v>0.105199220441902</v>
       </c>
@@ -8197,7 +8206,7 @@
       <c r="D51" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="E51" s="18" t="n">
+      <c r="E51" s="34" t="n">
         <f aca="false">INDEX(B25:B29,MATCH($A51,$A25:$A29,0))^C51*IF(C51=5,1,INDEX(B33:B37,MATCH($A51,$A25:$A29,0)))</f>
         <v>0.0617387924968411</v>
       </c>
@@ -8222,7 +8231,7 @@
       <c r="D52" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="E52" s="18" t="n">
+      <c r="E52" s="34" t="n">
         <f aca="false">INDEX(B25:B29,MATCH($A52,$A25:$A29,0))^C52*IF(C52=5,1,INDEX(B33:B37,MATCH($A52,$A25:$A29,0)))</f>
         <v>0.0696190428360652</v>
       </c>
@@ -8247,7 +8256,7 @@
       <c r="D53" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="E53" s="18" t="n">
+      <c r="E53" s="34" t="n">
         <f aca="false">INDEX(B25:B29,MATCH($A53,$A25:$A29,0))^C53*IF(C53=5,1,INDEX(B33:B37,MATCH($A53,$A25:$A29,0)))</f>
         <v>0.133105066484267</v>
       </c>
@@ -8272,7 +8281,7 @@
       <c r="D54" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="E54" s="18" t="n">
+      <c r="E54" s="34" t="n">
         <f aca="false">INDEX(B25:B29,MATCH($A54,$A25:$A29,0))^C54*IF(C54=5,1,INDEX(B33:B37,MATCH($A54,$A25:$A29,0)))</f>
         <v>0.0868510558809841</v>
       </c>
@@ -8297,7 +8306,7 @@
       <c r="D55" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="E55" s="18" t="n">
+      <c r="E55" s="34" t="n">
         <f aca="false">INDEX(B25:B29,MATCH($A55,$A25:$A29,0))^C55*IF(C55=5,1,INDEX(B33:B37,MATCH($A55,$A25:$A29,0)))</f>
         <v>0.118277620830176</v>
       </c>
@@ -8375,7 +8384,7 @@
       <c r="A61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="B61" s="24" t="n">
+      <c r="B61" s="35" t="n">
         <f aca="false">COMBIN($B$6*$B$7,A61)*($B$20/$B$8)^A61*(1-$B$20/$B$8)^($B$6*$B$7-A61)</f>
         <v>0.336700862051614</v>
       </c>
@@ -8394,7 +8403,7 @@
       <c r="A62" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B62" s="24" t="n">
+      <c r="B62" s="35" t="n">
         <f aca="false">COMBIN($B$6*$B$7,A62)*($B$20/$B$8)^A62*(1-$B$20/$B$8)^($B$6*$B$7-A62)</f>
         <v>0.380146134574403</v>
       </c>
@@ -8410,7 +8419,7 @@
       <c r="A63" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B63" s="24" t="n">
+      <c r="B63" s="35" t="n">
         <f aca="false">COMBIN($B$6*$B$7,A63)*($B$20/$B$8)^A63*(1-$B$20/$B$8)^($B$6*$B$7-A63)</f>
         <v>0.200292049399417</v>
       </c>
@@ -8426,7 +8435,7 @@
       <c r="A64" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B64" s="24" t="n">
+      <c r="B64" s="35" t="n">
         <f aca="false">COMBIN($B$6*$B$7,A64)*($B$20/$B$8)^A64*(1-$B$20/$B$8)^($B$6*$B$7-A64)</f>
         <v>0.0653282311661179</v>
       </c>
@@ -8442,7 +8451,7 @@
       <c r="A65" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B65" s="24" t="n">
+      <c r="B65" s="35" t="n">
         <f aca="false">COMBIN($B$6*$B$7,A65)*($B$20/$B$8)^A65*(1-$B$20/$B$8)^($B$6*$B$7-A65)</f>
         <v>0.0147515360697686</v>
       </c>
@@ -8458,7 +8467,7 @@
       <c r="A66" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B66" s="24" t="n">
+      <c r="B66" s="35" t="n">
         <f aca="false">COMBIN($B$6*$B$7,A66)*($B$20/$B$8)^A66*(1-$B$20/$B$8)^($B$6*$B$7-A66)</f>
         <v>0.00244272747821974</v>
       </c>
@@ -8474,7 +8483,7 @@
       <c r="A67" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B67" s="24" t="n">
+      <c r="B67" s="35" t="n">
         <f aca="false">COMBIN($B$6*$B$7,A67)*($B$20/$B$8)^A67*(1-$B$20/$B$8)^($B$6*$B$7-A67)</f>
         <v>0.000306435346730075</v>
       </c>
@@ -8490,7 +8499,7 @@
       <c r="A68" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B68" s="24" t="n">
+      <c r="B68" s="35" t="n">
         <f aca="false">COMBIN($B$6*$B$7,A68)*($B$20/$B$8)^A68*(1-$B$20/$B$8)^($B$6*$B$7-A68)</f>
         <v>2.96550335545234E-005</v>
       </c>
@@ -8506,7 +8515,7 @@
       <c r="A69" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B69" s="24" t="n">
+      <c r="B69" s="35" t="n">
         <f aca="false">COMBIN($B$6*$B$7,A69)*($B$20/$B$8)^A69*(1-$B$20/$B$8)^($B$6*$B$7-A69)</f>
         <v>2.23209929980284E-006</v>
       </c>
@@ -8522,7 +8531,7 @@
       <c r="A70" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B70" s="24" t="n">
+      <c r="B70" s="35" t="n">
         <f aca="false">COMBIN($B$6*$B$7,A70)*($B$20/$B$8)^A70*(1-$B$20/$B$8)^($B$6*$B$7-A70)</f>
         <v>1.30672479916773E-007</v>
       </c>
@@ -8538,7 +8547,7 @@
       <c r="A71" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B71" s="24" t="n">
+      <c r="B71" s="35" t="n">
         <f aca="false">COMBIN($B$6*$B$7,A71)*($B$20/$B$8)^A71*(1-$B$20/$B$8)^($B$6*$B$7-A71)</f>
         <v>5.90133780269298E-009</v>
       </c>
@@ -8554,7 +8563,7 @@
       <c r="A72" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B72" s="24" t="n">
+      <c r="B72" s="35" t="n">
         <f aca="false">COMBIN($B$6*$B$7,A72)*($B$20/$B$8)^A72*(1-$B$20/$B$8)^($B$6*$B$7-A72)</f>
         <v>2.01903052878059E-010</v>
       </c>
@@ -8570,7 +8579,7 @@
       <c r="A73" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B73" s="24" t="n">
+      <c r="B73" s="35" t="n">
         <f aca="false">COMBIN($B$6*$B$7,A73)*($B$20/$B$8)^A73*(1-$B$20/$B$8)^($B$6*$B$7-A73)</f>
         <v>5.06566799335632E-012</v>
       </c>
@@ -8586,7 +8595,7 @@
       <c r="A74" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B74" s="24" t="n">
+      <c r="B74" s="35" t="n">
         <f aca="false">COMBIN($B$6*$B$7,A74)*($B$20/$B$8)^A74*(1-$B$20/$B$8)^($B$6*$B$7-A74)</f>
         <v>8.79892703560651E-014</v>
       </c>
@@ -8602,7 +8611,7 @@
       <c r="A75" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B75" s="24" t="n">
+      <c r="B75" s="35" t="n">
         <f aca="false">COMBIN($B$6*$B$7,A75)*($B$20/$B$8)^A75*(1-$B$20/$B$8)^($B$6*$B$7-A75)</f>
         <v>9.46121186624356E-016</v>
       </c>
@@ -8618,7 +8627,7 @@
       <c r="A76" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B76" s="24" t="n">
+      <c r="B76" s="35" t="n">
         <f aca="false">COMBIN($B$6*$B$7,A76)*($B$20/$B$8)^A76*(1-$B$20/$B$8)^($B$6*$B$7-A76)</f>
         <v>4.74756150994301E-018</v>
       </c>
